--- a/data/trans_orig/P36BPD08_2023-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P36BPD08_2023-Habitat-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según el número de vasos de vino que consumen a la semana en 2023</t>
+          <t>Población según el número de vasos de vino que consumen a la semana en 2023 (tasa de respuesta: 99,84%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -730,12 +730,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>527947</t>
+          <t>526141</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>559674</t>
+          <t>558818</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -745,12 +745,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>83,5%</t>
+          <t>83,21%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>88,52%</t>
+          <t>88,38%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -765,12 +765,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>648221</t>
+          <t>647490</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>660845</t>
+          <t>660843</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -780,7 +780,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>95,98%</t>
+          <t>95,87%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1182332</t>
+          <t>1181903</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>1216811</t>
+          <t>1216219</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -815,12 +815,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>90,42%</t>
+          <t>90,38%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>93,05%</t>
+          <t>93,01%</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>16876</t>
+          <t>16673</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>33695</t>
+          <t>33657</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -858,12 +858,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>2,67%</t>
+          <t>2,64%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>5,33%</t>
+          <t>5,32%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>4806</t>
+          <t>4968</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>13700</t>
+          <t>13049</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -893,12 +893,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,74%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>2,03%</t>
+          <t>1,93%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>23776</t>
+          <t>22851</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>42983</t>
+          <t>41618</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>1,75%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>3,29%</t>
+          <t>3,18%</t>
         </is>
       </c>
     </row>
@@ -956,12 +956,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>51796</t>
+          <t>51059</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>79284</t>
+          <t>79413</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -971,12 +971,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>8,19%</t>
+          <t>8,08%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>12,54%</t>
+          <t>12,56%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -991,12 +991,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>7846</t>
+          <t>7945</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>18052</t>
+          <t>18195</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1006,12 +1006,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,18%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>2,67%</t>
+          <t>2,69%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1026,12 +1026,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>62373</t>
+          <t>60892</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>91432</t>
+          <t>90593</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1041,12 +1041,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>4,77%</t>
+          <t>4,66%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>6,99%</t>
+          <t>6,93%</t>
         </is>
       </c>
     </row>
@@ -1186,12 +1186,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>997466</t>
+          <t>995051</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1115550</t>
+          <t>1117483</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1201,12 +1201,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>83,77%</t>
+          <t>83,57%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>93,69%</t>
+          <t>93,85%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1221,12 +1221,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>915038</t>
+          <t>915154</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>933071</t>
+          <t>933957</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1236,12 +1236,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>95,5%</t>
+          <t>95,52%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>97,39%</t>
+          <t>97,48%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1256,12 +1256,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1931890</t>
+          <t>1933928</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>2028199</t>
+          <t>2028344</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1271,12 +1271,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>89,91%</t>
+          <t>90,0%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>94,39%</t>
+          <t>94,4%</t>
         </is>
       </c>
     </row>
@@ -1299,12 +1299,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>32849</t>
+          <t>33349</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>92804</t>
+          <t>91160</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1314,12 +1314,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>2,76%</t>
+          <t>2,8%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>7,79%</t>
+          <t>7,66%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1334,12 +1334,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>11394</t>
+          <t>11907</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>24320</t>
+          <t>25091</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1349,12 +1349,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>2,54%</t>
+          <t>2,62%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1369,12 +1369,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>52834</t>
+          <t>51576</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>107585</t>
+          <t>110452</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1384,12 +1384,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>2,46%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>5,01%</t>
+          <t>5,14%</t>
         </is>
       </c>
     </row>
@@ -1412,12 +1412,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>43592</t>
+          <t>41596</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>109668</t>
+          <t>113631</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1427,12 +1427,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>3,66%</t>
+          <t>3,49%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>9,21%</t>
+          <t>9,54%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1447,12 +1447,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>10929</t>
+          <t>10729</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>23076</t>
+          <t>24107</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1462,12 +1462,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>1,12%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2,41%</t>
+          <t>2,52%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1482,12 +1482,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>65761</t>
+          <t>67461</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>120676</t>
+          <t>119944</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1497,12 +1497,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>3,06%</t>
+          <t>3,14%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>5,62%</t>
+          <t>5,58%</t>
         </is>
       </c>
     </row>
@@ -1642,12 +1642,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>599585</t>
+          <t>599971</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>639165</t>
+          <t>639892</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1657,12 +1657,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>85,25%</t>
+          <t>85,3%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>90,87%</t>
+          <t>90,98%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1677,12 +1677,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>890341</t>
+          <t>888122</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>918946</t>
+          <t>918116</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1692,12 +1692,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>95,51%</t>
+          <t>95,27%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>98,58%</t>
+          <t>98,49%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1712,12 +1712,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1495474</t>
+          <t>1495438</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1563329</t>
+          <t>1560201</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1732,7 +1732,7 @@
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>95,58%</t>
+          <t>95,39%</t>
         </is>
       </c>
     </row>
@@ -1755,12 +1755,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>28976</t>
+          <t>28828</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>62774</t>
+          <t>63713</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1770,12 +1770,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,12%</t>
+          <t>4,1%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>8,92%</t>
+          <t>9,06%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1790,12 +1790,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>8432</t>
+          <t>9063</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>27891</t>
+          <t>28330</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1805,12 +1805,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2,99%</t>
+          <t>3,04%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1825,12 +1825,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>39153</t>
+          <t>38767</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>84311</t>
+          <t>83369</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1840,12 +1840,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,39%</t>
+          <t>2,37%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>5,15%</t>
+          <t>5,1%</t>
         </is>
       </c>
     </row>
@@ -1868,12 +1868,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>29362</t>
+          <t>29468</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>53530</t>
+          <t>51178</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1883,12 +1883,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>4,17%</t>
+          <t>4,19%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>7,61%</t>
+          <t>7,28%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1903,12 +1903,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>4481</t>
+          <t>5125</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>18920</t>
+          <t>20060</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1918,12 +1918,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,55%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>2,03%</t>
+          <t>2,15%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1938,12 +1938,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>32883</t>
+          <t>33288</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>67603</t>
+          <t>66988</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1953,12 +1953,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>2,04%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>4,13%</t>
+          <t>4,1%</t>
         </is>
       </c>
     </row>
@@ -2098,12 +2098,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>802068</t>
+          <t>803389</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>837760</t>
+          <t>839881</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2113,12 +2113,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>86,71%</t>
+          <t>86,85%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>90,57%</t>
+          <t>90,79%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2133,12 +2133,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1049516</t>
+          <t>1049793</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>1069769</t>
+          <t>1069496</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2148,12 +2148,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>95,91%</t>
+          <t>95,94%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>97,76%</t>
+          <t>97,74%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2168,12 +2168,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1860041</t>
+          <t>1858476</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1904132</t>
+          <t>1904408</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2183,12 +2183,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>92,11%</t>
+          <t>92,04%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>94,3%</t>
+          <t>94,31%</t>
         </is>
       </c>
     </row>
@@ -2211,12 +2211,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>22023</t>
+          <t>22975</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>44124</t>
+          <t>44976</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2226,49 +2226,49 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
+          <t>2,48%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>4,86%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>18107</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>12117</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>26037</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>1,65%</t>
+        </is>
+      </c>
+      <c r="O17" s="2" t="inlineStr">
+        <is>
+          <t>1,11%</t>
+        </is>
+      </c>
+      <c r="P17" s="2" t="inlineStr">
+        <is>
           <t>2,38%</t>
         </is>
       </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>4,77%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>18107</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>11430</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>25748</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>1,65%</t>
-        </is>
-      </c>
-      <c r="O17" s="2" t="inlineStr">
-        <is>
-          <t>1,04%</t>
-        </is>
-      </c>
-      <c r="P17" s="2" t="inlineStr">
-        <is>
-          <t>2,35%</t>
-        </is>
-      </c>
       <c r="Q17" s="2" t="inlineStr">
         <is>
           <t>68</t>
@@ -2281,12 +2281,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>37803</t>
+          <t>38577</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>64992</t>
+          <t>64893</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2296,12 +2296,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>1,87%</t>
+          <t>1,91%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>3,22%</t>
+          <t>3,21%</t>
         </is>
       </c>
     </row>
@@ -2324,12 +2324,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>59414</t>
+          <t>57563</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>89053</t>
+          <t>87586</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>6,42%</t>
+          <t>6,22%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>9,63%</t>
+          <t>9,47%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2359,12 +2359,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>9469</t>
+          <t>9628</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>23498</t>
+          <t>23852</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2374,12 +2374,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>0,88%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>2,18%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2394,12 +2394,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>72149</t>
+          <t>72499</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>106491</t>
+          <t>105885</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2409,12 +2409,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>3,57%</t>
+          <t>3,59%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>5,27%</t>
+          <t>5,24%</t>
         </is>
       </c>
     </row>
@@ -2554,12 +2554,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>2977203</t>
+          <t>2980225</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>3127482</t>
+          <t>3136197</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2569,12 +2569,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>86,26%</t>
+          <t>86,35%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>90,62%</t>
+          <t>90,87%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2589,12 +2589,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>3522376</t>
+          <t>3522576</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>3567345</t>
+          <t>3567237</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2604,7 +2604,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>96,24%</t>
+          <t>96,25%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2619,17 +2619,17 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>6577630</t>
+          <t>6577631</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>6520156</t>
+          <t>6521436</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>6651074</t>
+          <t>6649045</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2639,12 +2639,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>91,69%</t>
+          <t>91,71%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>93,53%</t>
+          <t>93,5%</t>
         </is>
       </c>
     </row>
@@ -2667,12 +2667,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>118028</t>
+          <t>123873</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>194280</t>
+          <t>196118</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2682,12 +2682,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>3,42%</t>
+          <t>3,59%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>5,63%</t>
+          <t>5,68%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2702,12 +2702,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>47191</t>
+          <t>49209</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>75865</t>
+          <t>76199</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2717,12 +2717,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,34%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>2,08%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2737,12 +2737,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>184075</t>
+          <t>185455</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>256138</t>
+          <t>259999</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2752,12 +2752,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>2,59%</t>
+          <t>2,61%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>3,66%</t>
         </is>
       </c>
     </row>
@@ -2780,12 +2780,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>199087</t>
+          <t>196775</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>293360</t>
+          <t>292243</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2795,12 +2795,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>5,77%</t>
+          <t>5,7%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>8,5%</t>
+          <t>8,47%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2815,12 +2815,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>41912</t>
+          <t>42223</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>69937</t>
+          <t>70939</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2835,7 +2835,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>1,94%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2850,12 +2850,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>266346</t>
+          <t>267560</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>348439</t>
+          <t>350513</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2865,12 +2865,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>3,75%</t>
+          <t>3,76%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>4,9%</t>
+          <t>4,93%</t>
         </is>
       </c>
     </row>
@@ -2958,17 +2958,17 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>7111232</t>
+          <t>7111233</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>7111232</t>
+          <t>7111233</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>7111232</t>
+          <t>7111233</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">

--- a/data/trans_orig/P36BPD08_2023-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P36BPD08_2023-Habitat-trans_orig.xlsx
@@ -725,32 +725,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>545008</t>
+          <t>590878</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>526141</t>
+          <t>574104</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>558818</t>
+          <t>606521</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>86,2%</t>
+          <t>85,98%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>83,21%</t>
+          <t>83,53%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>88,38%</t>
+          <t>88,25%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -760,32 +760,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>655303</t>
+          <t>709155</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>647490</t>
+          <t>700371</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>660843</t>
+          <t>715675</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>97,03%</t>
+          <t>96,78%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>95,87%</t>
+          <t>95,58%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>97,85%</t>
+          <t>97,67%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>1200311</t>
+          <t>1300033</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1181903</t>
+          <t>1278700</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>1216219</t>
+          <t>1318110</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>91,79%</t>
+          <t>91,55%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>90,38%</t>
+          <t>90,05%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>93,01%</t>
+          <t>92,83%</t>
         </is>
       </c>
     </row>
@@ -838,32 +838,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>23401</t>
+          <t>24265</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>16673</t>
+          <t>16851</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>33657</t>
+          <t>34368</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>3,7%</t>
+          <t>3,53%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>2,64%</t>
+          <t>2,45%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>5,32%</t>
+          <t>5,0%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>8133</t>
+          <t>10305</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>4968</t>
+          <t>6024</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>13049</t>
+          <t>15861</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,41%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,82%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>1,93%</t>
+          <t>2,16%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>31534</t>
+          <t>34570</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>22851</t>
+          <t>25465</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>41618</t>
+          <t>46064</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>2,41%</t>
+          <t>2,43%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>1,79%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>3,18%</t>
+          <t>3,24%</t>
         </is>
       </c>
     </row>
@@ -951,32 +951,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>63859</t>
+          <t>72122</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>51059</t>
+          <t>58136</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>79413</t>
+          <t>87728</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>10,1%</t>
+          <t>10,49%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>8,08%</t>
+          <t>8,46%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>12,56%</t>
+          <t>12,76%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>11934</t>
+          <t>13263</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>7945</t>
+          <t>8717</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>18195</t>
+          <t>20438</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>1,77%</t>
+          <t>1,81%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>2,69%</t>
+          <t>2,79%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>75794</t>
+          <t>85384</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>60892</t>
+          <t>69937</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>90593</t>
+          <t>103072</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>5,8%</t>
+          <t>6,01%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>4,66%</t>
+          <t>4,93%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>6,93%</t>
+          <t>7,26%</t>
         </is>
       </c>
     </row>
@@ -1064,17 +1064,17 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>632269</t>
+          <t>687265</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>632269</t>
+          <t>687265</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>632269</t>
+          <t>687265</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1099,17 +1099,17 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>675370</t>
+          <t>732722</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>675370</t>
+          <t>732722</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>675370</t>
+          <t>732722</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1134,17 +1134,17 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>1307639</t>
+          <t>1419987</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1307639</t>
+          <t>1419987</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>1307639</t>
+          <t>1419987</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1181,32 +1181,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>1045973</t>
+          <t>889196</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>995051</t>
+          <t>860133</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1117483</t>
+          <t>912631</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>87,85%</t>
+          <t>84,96%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>83,57%</t>
+          <t>82,18%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>93,85%</t>
+          <t>87,2%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1216,32 +1216,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>925145</t>
+          <t>1033784</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>915154</t>
+          <t>1023049</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>933957</t>
+          <t>1041835</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>96,56%</t>
+          <t>96,54%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>95,52%</t>
+          <t>95,54%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>97,48%</t>
+          <t>97,29%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1251,32 +1251,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>1971117</t>
+          <t>1922980</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1933928</t>
+          <t>1891155</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>2028344</t>
+          <t>1947677</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>91,73%</t>
+          <t>90,82%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>90,0%</t>
+          <t>89,31%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>94,4%</t>
+          <t>91,98%</t>
         </is>
       </c>
     </row>
@@ -1294,32 +1294,32 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>63146</t>
+          <t>65432</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>33349</t>
+          <t>49036</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>91160</t>
+          <t>89003</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>5,3%</t>
+          <t>6,25%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>4,69%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>7,66%</t>
+          <t>8,5%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1329,22 +1329,22 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>17203</t>
+          <t>19513</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>11907</t>
+          <t>13316</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>25091</t>
+          <t>28621</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>1,82%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
@@ -1354,7 +1354,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>2,62%</t>
+          <t>2,67%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1364,32 +1364,32 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>80349</t>
+          <t>84945</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>51576</t>
+          <t>64972</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>110452</t>
+          <t>107028</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>3,74%</t>
+          <t>4,01%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>3,07%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>5,14%</t>
+          <t>5,05%</t>
         </is>
       </c>
     </row>
@@ -1407,32 +1407,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>81535</t>
+          <t>91970</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>41596</t>
+          <t>75704</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>113631</t>
+          <t>110981</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>6,85%</t>
+          <t>8,79%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>3,49%</t>
+          <t>7,23%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>9,54%</t>
+          <t>10,6%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1442,17 +1442,17 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>15758</t>
+          <t>17542</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>10729</t>
+          <t>11853</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>24107</t>
+          <t>26413</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1462,12 +1462,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,11%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2,52%</t>
+          <t>2,47%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1477,32 +1477,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>97294</t>
+          <t>109512</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>67461</t>
+          <t>90264</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>119944</t>
+          <t>130844</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>4,53%</t>
+          <t>5,17%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>3,14%</t>
+          <t>4,26%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>5,58%</t>
+          <t>6,18%</t>
         </is>
       </c>
     </row>
@@ -1520,17 +1520,17 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1190654</t>
+          <t>1046598</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1190654</t>
+          <t>1046598</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>1190654</t>
+          <t>1046598</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1555,17 +1555,17 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>958106</t>
+          <t>1070838</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>958106</t>
+          <t>1070838</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>958106</t>
+          <t>1070838</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1590,17 +1590,17 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>2148760</t>
+          <t>2117436</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>2148760</t>
+          <t>2117436</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>2148760</t>
+          <t>2117436</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1637,32 +1637,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>621652</t>
+          <t>712530</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>599971</t>
+          <t>690228</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>639892</t>
+          <t>730928</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>88,38%</t>
+          <t>88,87%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>85,3%</t>
+          <t>86,09%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>90,98%</t>
+          <t>91,17%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1672,32 +1672,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>902447</t>
+          <t>777446</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>888122</t>
+          <t>766325</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>918116</t>
+          <t>786409</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>96,81%</t>
+          <t>95,85%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>95,27%</t>
+          <t>94,48%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>98,49%</t>
+          <t>96,96%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1707,32 +1707,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>1524101</t>
+          <t>1489976</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1495438</t>
+          <t>1465147</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1560201</t>
+          <t>1509368</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>93,18%</t>
+          <t>92,38%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>91,43%</t>
+          <t>90,84%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>95,39%</t>
+          <t>93,58%</t>
         </is>
       </c>
     </row>
@@ -1750,32 +1750,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>42182</t>
+          <t>44305</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>28828</t>
+          <t>30341</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>63713</t>
+          <t>62046</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>6,0%</t>
+          <t>5,53%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,1%</t>
+          <t>3,78%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>9,06%</t>
+          <t>7,74%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1785,32 +1785,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>18014</t>
+          <t>20363</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>9063</t>
+          <t>13855</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>28330</t>
+          <t>28654</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>1,93%</t>
+          <t>2,51%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>1,71%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>3,04%</t>
+          <t>3,53%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1820,32 +1820,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>60195</t>
+          <t>64668</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>38767</t>
+          <t>48712</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>83369</t>
+          <t>84972</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>3,68%</t>
+          <t>4,01%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,37%</t>
+          <t>3,02%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>5,1%</t>
+          <t>5,27%</t>
         </is>
       </c>
     </row>
@@ -1863,32 +1863,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>39526</t>
+          <t>44906</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>29468</t>
+          <t>33826</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>51178</t>
+          <t>59290</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>5,62%</t>
+          <t>5,6%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>4,19%</t>
+          <t>4,22%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>7,28%</t>
+          <t>7,4%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1898,32 +1898,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>11749</t>
+          <t>13292</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>5125</t>
+          <t>7848</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>20060</t>
+          <t>20826</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,64%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>2,57%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1933,32 +1933,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>51275</t>
+          <t>58197</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>33288</t>
+          <t>44987</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>66988</t>
+          <t>74079</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>3,14%</t>
+          <t>3,61%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>2,04%</t>
+          <t>2,79%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>4,1%</t>
+          <t>4,59%</t>
         </is>
       </c>
     </row>
@@ -1976,17 +1976,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>703360</t>
+          <t>801741</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>703360</t>
+          <t>801741</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>703360</t>
+          <t>801741</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2011,17 +2011,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>932210</t>
+          <t>811100</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>932210</t>
+          <t>811100</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>932210</t>
+          <t>811100</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2046,17 +2046,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>1635571</t>
+          <t>1612841</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>1635571</t>
+          <t>1612841</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>1635571</t>
+          <t>1612841</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2093,32 +2093,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>821544</t>
+          <t>879481</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>803389</t>
+          <t>859207</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>839881</t>
+          <t>897361</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>88,81%</t>
+          <t>89,08%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>86,85%</t>
+          <t>87,03%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>90,79%</t>
+          <t>90,89%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2128,32 +2128,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>1060557</t>
+          <t>1078353</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1049793</t>
+          <t>1065954</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>1069496</t>
+          <t>1088075</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>96,92%</t>
+          <t>96,51%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>95,94%</t>
+          <t>95,4%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>97,74%</t>
+          <t>97,38%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2163,32 +2163,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>1882101</t>
+          <t>1957835</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1858476</t>
+          <t>1934000</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1904408</t>
+          <t>1977858</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>93,21%</t>
+          <t>93,02%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>92,04%</t>
+          <t>91,89%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>94,31%</t>
+          <t>93,98%</t>
         </is>
       </c>
     </row>
@@ -2206,32 +2206,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>31663</t>
+          <t>32758</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>22975</t>
+          <t>23110</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>44976</t>
+          <t>45014</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>3,42%</t>
+          <t>3,32%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>2,48%</t>
+          <t>2,34%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>4,86%</t>
+          <t>4,56%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2241,32 +2241,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>18107</t>
+          <t>19177</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>12117</t>
+          <t>12880</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>26037</t>
+          <t>27338</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>1,72%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>1,15%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>2,38%</t>
+          <t>2,45%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2276,32 +2276,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>49770</t>
+          <t>51935</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>38577</t>
+          <t>39754</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>64893</t>
+          <t>65588</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>2,46%</t>
+          <t>2,47%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>1,89%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>3,21%</t>
+          <t>3,12%</t>
         </is>
       </c>
     </row>
@@ -2319,32 +2319,32 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>71825</t>
+          <t>75040</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>57563</t>
+          <t>61036</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>87586</t>
+          <t>92413</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>7,76%</t>
+          <t>7,6%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>6,22%</t>
+          <t>6,18%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>9,47%</t>
+          <t>9,36%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2354,32 +2354,32 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>15566</t>
+          <t>19842</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>9628</t>
+          <t>12600</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>23852</t>
+          <t>30682</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,78%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>1,13%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>2,18%</t>
+          <t>2,75%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2389,32 +2389,32 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>87391</t>
+          <t>94882</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>72499</t>
+          <t>77496</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>105885</t>
+          <t>117093</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>4,33%</t>
+          <t>4,51%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>3,59%</t>
+          <t>3,68%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>5,24%</t>
+          <t>5,56%</t>
         </is>
       </c>
     </row>
@@ -2432,17 +2432,17 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>925033</t>
+          <t>987279</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>925033</t>
+          <t>987279</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>925033</t>
+          <t>987279</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2467,17 +2467,17 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>1094229</t>
+          <t>1117372</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>1094229</t>
+          <t>1117372</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>1094229</t>
+          <t>1117372</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2502,17 +2502,17 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>2019262</t>
+          <t>2104652</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>2019262</t>
+          <t>2104652</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>2019262</t>
+          <t>2104652</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2549,32 +2549,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>3034178</t>
+          <t>3072085</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>2980225</t>
+          <t>3027867</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>3136197</t>
+          <t>3108403</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>87,91%</t>
+          <t>87,2%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>86,35%</t>
+          <t>85,95%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>90,87%</t>
+          <t>88,23%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2584,32 +2584,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>3543453</t>
+          <t>3598737</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>3522576</t>
+          <t>3577598</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>3567237</t>
+          <t>3616682</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>96,82%</t>
+          <t>96,43%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>96,25%</t>
+          <t>95,86%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>97,47%</t>
+          <t>96,91%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2619,32 +2619,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>6577631</t>
+          <t>6670822</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>6521436</t>
+          <t>6618733</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>6649045</t>
+          <t>6716431</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>92,5%</t>
+          <t>91,95%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>91,71%</t>
+          <t>91,23%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>93,5%</t>
+          <t>92,58%</t>
         </is>
       </c>
     </row>
@@ -2662,32 +2662,32 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>160392</t>
+          <t>166761</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>123873</t>
+          <t>139503</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>196118</t>
+          <t>197903</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>4,65%</t>
+          <t>4,73%</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>3,59%</t>
+          <t>3,96%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>5,68%</t>
+          <t>5,62%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2697,32 +2697,32 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>61456</t>
+          <t>69357</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>49209</t>
+          <t>56763</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>76199</t>
+          <t>83019</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>1,86%</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,52%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>2,22%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2732,32 +2732,32 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>221848</t>
+          <t>236118</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>185455</t>
+          <t>207006</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>259999</t>
+          <t>271017</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t>3,12%</t>
+          <t>3,25%</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>2,61%</t>
+          <t>2,85%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>3,66%</t>
+          <t>3,74%</t>
         </is>
       </c>
     </row>
@@ -2775,32 +2775,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>256747</t>
+          <t>284037</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>196775</t>
+          <t>255306</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>292243</t>
+          <t>318845</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>7,44%</t>
+          <t>8,06%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>5,7%</t>
+          <t>7,25%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>8,47%</t>
+          <t>9,05%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2810,32 +2810,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>55007</t>
+          <t>63938</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>42223</t>
+          <t>51584</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>70939</t>
+          <t>78282</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,71%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,38%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>2,1%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2845,32 +2845,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>311754</t>
+          <t>347975</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>267560</t>
+          <t>314030</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>350513</t>
+          <t>385890</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>4,38%</t>
+          <t>4,8%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>3,76%</t>
+          <t>4,33%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>4,93%</t>
+          <t>5,32%</t>
         </is>
       </c>
     </row>
@@ -2888,17 +2888,17 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>3451317</t>
+          <t>3522883</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3451317</t>
+          <t>3522883</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3451317</t>
+          <t>3522883</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2923,17 +2923,17 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>3659916</t>
+          <t>3732032</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>3659916</t>
+          <t>3732032</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3659916</t>
+          <t>3732032</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2958,17 +2958,17 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>7111233</t>
+          <t>7254915</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>7111233</t>
+          <t>7254915</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>7111233</t>
+          <t>7254915</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
